--- a/system_design/Georgetown/V0.5.2/bill_of_materials.xlsx
+++ b/system_design/Georgetown/V0.5.2/bill_of_materials.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/asifuzzaman_sc_edu/Documents/Github Repos/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5.2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="148" documentId="13_ncr:1_{92FC9251-22EE-4CB6-81B0-D0434CABC585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C6E9F23-6314-4B84-BFD3-4D7966CD93F5}"/>
+  <xr:revisionPtr revIDLastSave="151" documentId="13_ncr:1_{92FC9251-22EE-4CB6-81B0-D0434CABC585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A22FF58F-C98B-49F2-8610-E9AF52551917}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="151">
   <si>
     <t>Arduino Nano</t>
   </si>
@@ -371,9 +371,6 @@
     <t xml:space="preserve"> BME280 environmental sensor</t>
   </si>
   <si>
-    <t xml:space="preserve">U3 (INA219) </t>
-  </si>
-  <si>
     <t>BT1  (coin cell holder)</t>
   </si>
   <si>
@@ -486,6 +483,12 @@
   </si>
   <si>
     <t>MMBT2222A NPN transistor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U3 </t>
+  </si>
+  <si>
+    <t>PCB stage height v0.5.2</t>
   </si>
 </sst>
 </file>
@@ -932,7 +935,7 @@
   <sheetData>
     <row r="1" spans="1:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>15</v>
@@ -941,7 +944,7 @@
         <v>16</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>17</v>
@@ -979,7 +982,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E2" s="3">
         <v>25.7</v>
@@ -1000,7 +1003,7 @@
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>107</v>
@@ -1009,7 +1012,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E3" s="3">
         <v>2.52</v>
@@ -1036,7 +1039,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E4" s="3">
         <v>1.4</v>
@@ -1057,7 +1060,7 @@
     </row>
     <row r="5" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>108</v>
@@ -1066,7 +1069,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E5" s="3">
         <v>11.96</v>
@@ -1093,7 +1096,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E6" s="3">
         <v>5.26</v>
@@ -1114,16 +1117,16 @@
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E7" s="3">
         <v>4.95</v>
@@ -1133,10 +1136,10 @@
         <v>4.95</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1150,7 +1153,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E8" s="3">
         <v>15.2</v>
@@ -1174,7 +1177,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E9" s="3">
         <v>5.25</v>
@@ -1204,7 +1207,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E10" s="3">
         <v>18</v>
@@ -1234,7 +1237,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E11" s="3">
         <v>1.0900000000000001</v>
@@ -1252,7 +1255,7 @@
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>9</v>
@@ -1261,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E12" s="3">
         <v>0.57999999999999996</v>
@@ -1279,16 +1282,16 @@
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C13" s="2">
-        <v>1</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="E13" s="3">
         <v>0.14000000000000001</v>
@@ -1298,10 +1301,13 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>150</v>
+      </c>
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
@@ -1309,7 +1315,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E14" s="3">
         <v>8.23</v>
@@ -1327,13 +1333,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C15" s="2">
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E15" s="3">
         <v>8.24</v>
@@ -1363,16 +1369,16 @@
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="C16" s="2">
         <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E16" s="3">
         <v>2.0299999999999998</v>
@@ -1390,7 +1396,7 @@
     </row>
     <row r="17" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>101</v>
@@ -1399,7 +1405,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E17" s="3">
         <v>0.2</v>
@@ -1417,16 +1423,16 @@
     </row>
     <row r="18" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="C18" s="2">
         <v>3</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E18" s="3">
         <v>0.1</v>
@@ -1436,7 +1442,7 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1450,7 +1456,7 @@
         <v>3</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E19" s="3">
         <v>0.1</v>
@@ -1477,7 +1483,7 @@
         <v>4</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E20" s="3">
         <v>0.1</v>
@@ -1495,16 +1501,16 @@
     </row>
     <row r="21" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="C21" s="2">
         <v>2</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E21" s="3">
         <v>0.1</v>
@@ -1514,7 +1520,7 @@
         <v>0.2</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1528,7 +1534,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E22" s="3">
         <v>0.39</v>
@@ -1555,7 +1561,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E23" s="3">
         <v>0.41</v>
@@ -1582,7 +1588,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E24" s="3">
         <v>0.26</v>
@@ -1600,7 +1606,7 @@
     </row>
     <row r="25" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>33</v>
@@ -1609,7 +1615,7 @@
         <v>4</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E25" s="3">
         <v>0.48</v>
@@ -1636,7 +1642,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E26" s="3">
         <v>3.58</v>
@@ -1666,7 +1672,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E27" s="3">
         <v>60.76</v>
@@ -1684,13 +1690,13 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C28" s="2">
         <v>1</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E28" s="3">
         <v>0.91</v>
@@ -1708,7 +1714,7 @@
     </row>
     <row r="29" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>38</v>
@@ -1717,7 +1723,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E29" s="3">
         <v>2.15</v>
@@ -1735,16 +1741,16 @@
     </row>
     <row r="30" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C30" s="2">
         <v>1</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E30" s="3">
         <v>0.1</v>
@@ -1754,21 +1760,21 @@
         <v>0.1</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C31" s="2">
         <v>1</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E31" s="3">
         <v>0.13</v>
@@ -1795,7 +1801,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E32" s="3">
         <v>7.39</v>
@@ -1810,13 +1816,13 @@
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C33" s="2">
         <v>2</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E33" s="3">
         <v>0.01</v>
@@ -1829,13 +1835,13 @@
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C34" s="2">
         <v>2</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E34" s="3">
         <v>0.01</v>
@@ -1848,13 +1854,13 @@
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C35" s="2">
         <v>2</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E35" s="3">
         <v>0.01</v>
@@ -1864,18 +1870,18 @@
         <v>0.02</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C36" s="2">
         <v>4</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E36" s="3">
         <v>7.2999999999999995E-2</v>
@@ -1893,13 +1899,13 @@
         <v>90</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C37" s="2">
         <v>1</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E37" s="3">
         <v>2.68</v>
@@ -1909,7 +1915,7 @@
         <v>2.68</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1923,7 +1929,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E38" s="3">
         <v>25</v>

--- a/system_design/Georgetown/V0.5.2/bill_of_materials.xlsx
+++ b/system_design/Georgetown/V0.5.2/bill_of_materials.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/asifuzzaman_sc_edu/Documents/Github Repos/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5.2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\SWaP-Constrained-UAV-deployable-Water-Level-Sensor\system_design\Georgetown\V0.5.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="151" documentId="13_ncr:1_{92FC9251-22EE-4CB6-81B0-D0434CABC585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A22FF58F-C98B-49F2-8610-E9AF52551917}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ADAA0EB-7F46-452A-86E2-E40C43A33CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-16320" yWindow="-6540" windowWidth="16440" windowHeight="28320" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -917,23 +917,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="89.90625" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.54296875" customWidth="1"/>
-    <col min="5" max="5" width="13.08984375" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" customWidth="1"/>
-    <col min="7" max="7" width="69.453125" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="89.85546875" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.5703125" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="7" max="7" width="69.42578125" customWidth="1"/>
     <col min="8" max="8" width="76" customWidth="1"/>
-    <col min="9" max="9" width="83.54296875" customWidth="1"/>
-    <col min="10" max="10" width="62.54296875" customWidth="1"/>
-    <col min="11" max="11" width="55.81640625" customWidth="1"/>
+    <col min="9" max="9" width="83.5703125" customWidth="1"/>
+    <col min="10" max="10" width="62.5703125" customWidth="1"/>
+    <col min="11" max="11" width="55.85546875" customWidth="1"/>
     <col min="12" max="12" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>117</v>
       </c>
@@ -971,7 +971,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>123</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>122</v>
       </c>
@@ -1085,7 +1085,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>109</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>149</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>111</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>145</v>
       </c>
@@ -1304,7 +1304,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>150</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
@@ -1367,7 +1367,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>112</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>119</v>
       </c>
@@ -1421,7 +1421,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>141</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>102</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>103</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>138</v>
       </c>
@@ -1523,7 +1523,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>104</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>105</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>100</v>
       </c>
@@ -1604,7 +1604,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>144</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>106</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>44</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>13</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>114</v>
       </c>
@@ -1739,7 +1739,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>131</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>134</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>39</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
         <v>129</v>
       </c>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G33" s="1"/>
     </row>
-    <row r="34" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
         <v>130</v>
       </c>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
         <v>127</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="36" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
         <v>128</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="37" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>90</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="38" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>93</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E39" s="4" t="s">
         <v>14</v>
       </c>

--- a/system_design/Georgetown/V0.5.2/bill_of_materials.xlsx
+++ b/system_design/Georgetown/V0.5.2/bill_of_materials.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/asifuzzaman_sc_edu/Documents/Github Repos/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5.2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="151" documentId="13_ncr:1_{92FC9251-22EE-4CB6-81B0-D0434CABC585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A22FF58F-C98B-49F2-8610-E9AF52551917}"/>
+  <xr:revisionPtr revIDLastSave="152" documentId="13_ncr:1_{92FC9251-22EE-4CB6-81B0-D0434CABC585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A052D1E6-935E-43B0-8535-340BE751AB8E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -1051,7 +1051,7 @@
       <c r="G4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>56</v>
       </c>
       <c r="I4" s="2" t="s">
@@ -1999,8 +1999,9 @@
     <hyperlink ref="G21" r:id="rId44" xr:uid="{F2FBC813-F21B-4CA5-94D5-A1D3C7097891}"/>
     <hyperlink ref="G13" r:id="rId45" xr:uid="{0C1E97B9-B29C-4292-84AE-9AEFCCB0C868}"/>
     <hyperlink ref="G18" r:id="rId46" xr:uid="{51407470-A2C9-4C4E-89CA-FC24B70AF5A7}"/>
+    <hyperlink ref="H4" r:id="rId47" xr:uid="{1A2534D8-294F-4B39-89B1-8168C50C4225}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId47"/>
+  <pageSetup orientation="portrait" r:id="rId48"/>
 </worksheet>
 </file>
--- a/system_design/Georgetown/V0.5.2/bill_of_materials.xlsx
+++ b/system_design/Georgetown/V0.5.2/bill_of_materials.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/asifuzzaman_sc_edu/Documents/Github Repos/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5.2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="152" documentId="13_ncr:1_{92FC9251-22EE-4CB6-81B0-D0434CABC585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A052D1E6-935E-43B0-8535-340BE751AB8E}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="13_ncr:1_{92FC9251-22EE-4CB6-81B0-D0434CABC585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16017D9A-CC87-4B19-B7AA-AB5B1D921B2D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="152">
   <si>
     <t>Arduino Nano</t>
   </si>
@@ -489,6 +489,9 @@
   </si>
   <si>
     <t>PCB stage height v0.5.2</t>
+  </si>
+  <si>
+    <t>https://protosupplies.com/product/bme280-i2c-pressure-humidity-temperature-sensor-module/</t>
   </si>
 </sst>
 </file>
@@ -1114,6 +1117,9 @@
       <c r="I6" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="K6" s="1" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
@@ -2000,8 +2006,9 @@
     <hyperlink ref="G13" r:id="rId45" xr:uid="{0C1E97B9-B29C-4292-84AE-9AEFCCB0C868}"/>
     <hyperlink ref="G18" r:id="rId46" xr:uid="{51407470-A2C9-4C4E-89CA-FC24B70AF5A7}"/>
     <hyperlink ref="H4" r:id="rId47" xr:uid="{1A2534D8-294F-4B39-89B1-8168C50C4225}"/>
+    <hyperlink ref="K6" r:id="rId48" xr:uid="{3B26DD18-290E-4BFE-BB80-46E0A92D8884}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId48"/>
+  <pageSetup orientation="portrait" r:id="rId49"/>
 </worksheet>
 </file>
--- a/system_design/Georgetown/V0.5.2/bill_of_materials.xlsx
+++ b/system_design/Georgetown/V0.5.2/bill_of_materials.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/asifuzzaman_sc_edu/Documents/Github Repos/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5.2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\SWaP-Constrained-UAV-deployable-Water-Level-Sensor\system_design\Georgetown\V0.5.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="13_ncr:1_{92FC9251-22EE-4CB6-81B0-D0434CABC585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16017D9A-CC87-4B19-B7AA-AB5B1D921B2D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03FB38C-2BB2-4F7F-8258-5EC3F0FCDEF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="154">
   <si>
     <t>Arduino Nano</t>
   </si>
@@ -389,9 +389,6 @@
     <t>SSA-104-W-T,  4 pin connector</t>
   </si>
   <si>
-    <t>PCB Designator</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 8GB Micro SD Card</t>
   </si>
   <si>
@@ -492,6 +489,15 @@
   </si>
   <si>
     <t>https://protosupplies.com/product/bme280-i2c-pressure-humidity-temperature-sensor-module/</t>
+  </si>
+  <si>
+    <t>Part Designator</t>
+  </si>
+  <si>
+    <t>manufacturer part number</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.us/item/3256807913818826.html?src=google&amp;src=google&amp;albch=shopping&amp;acnt=708-803-3821&amp;isdl=y&amp;slnk=&amp;plac=&amp;mtctp=&amp;albbt=Google_7_shopping&amp;aff_platform=google&amp;aff_short_key=UneMJZVf&amp;gclsrc=aw.ds&amp;albagn=888888&amp;ds_e_adid=&amp;ds_e_matchtype=&amp;ds_e_device=c&amp;ds_e_network=x&amp;ds_e_product_group_id=&amp;ds_e_product_id=en3256807913818826&amp;ds_e_product_merchant_id=5343266820&amp;ds_e_product_country=US&amp;ds_e_product_language=en&amp;ds_e_product_channel=online&amp;ds_e_product_store_id=&amp;ds_url_v=2&amp;albcp=19558607238&amp;albag=&amp;isSmbAutoCall=false&amp;needSmbHouyi=false&amp;gad_source=1&amp;gad_campaignid=19566915268&amp;gbraid=0AAAAAD6I-hE1DxC2gZnFOXHh1kEusbMcy&amp;gclid=CjwKCAjwsfzSBhB5EiwAOGyqSRU193oQHDmqvw43tZsck5IFRgE9x0LpmqXCbfoW00kjTDmN2fMHGhoCCf0QAvD_BwE&amp;gatewayAdapt=glo2usa</t>
   </si>
 </sst>
 </file>
@@ -919,1096 +925,1104 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:M39"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="89.90625" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.54296875" customWidth="1"/>
-    <col min="5" max="5" width="13.08984375" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" customWidth="1"/>
-    <col min="7" max="7" width="69.453125" customWidth="1"/>
-    <col min="8" max="8" width="76" customWidth="1"/>
-    <col min="9" max="9" width="83.54296875" customWidth="1"/>
-    <col min="10" max="10" width="62.54296875" customWidth="1"/>
-    <col min="11" max="11" width="55.81640625" customWidth="1"/>
-    <col min="12" max="12" width="51" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.42578125" customWidth="1"/>
+    <col min="3" max="3" width="89.85546875" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.5703125" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="69.42578125" customWidth="1"/>
+    <col min="9" max="9" width="76" customWidth="1"/>
+    <col min="10" max="10" width="83.5703125" customWidth="1"/>
+    <col min="11" max="11" width="62.5703125" customWidth="1"/>
+    <col min="12" max="12" width="55.85546875" customWidth="1"/>
+    <col min="13" max="13" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>125</v>
-      </c>
       <c r="E1" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F2" s="3">
         <v>25.7</v>
       </c>
-      <c r="F2" s="3">
-        <f>C2*E2</f>
+      <c r="G2" s="3">
+        <f>D2*F2</f>
         <v>25.7</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="2">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F3" s="3">
         <v>2.52</v>
       </c>
-      <c r="F3" s="3">
-        <f t="shared" ref="F3:F38" si="0">C3*E3</f>
+      <c r="G3" s="3">
+        <f t="shared" ref="G3:G38" si="0">D3*F3</f>
         <v>2.52</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4" s="3">
         <v>1.4</v>
       </c>
-      <c r="F4" s="3">
+      <c r="G4" s="3">
         <f t="shared" si="0"/>
         <v>1.4</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F5" s="3">
         <v>11.96</v>
       </c>
-      <c r="F5" s="3">
+      <c r="G5" s="3">
         <f t="shared" si="0"/>
         <v>11.96</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C6" s="2">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F6" s="3">
         <v>5.26</v>
       </c>
-      <c r="F6" s="3">
+      <c r="G6" s="3">
         <f t="shared" si="0"/>
         <v>5.26</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="J6" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L6" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" s="3">
+        <v>4.95</v>
+      </c>
+      <c r="G7" s="3">
+        <f t="shared" si="0"/>
+        <v>4.95</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C7" s="2">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E7" s="3">
-        <v>4.95</v>
-      </c>
-      <c r="F7" s="3">
-        <f t="shared" si="0"/>
-        <v>4.95</v>
-      </c>
-      <c r="G7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="2">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F8" s="3">
         <v>15.2</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <f t="shared" si="0"/>
         <v>15.2</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="2">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F9" s="3">
         <v>5.25</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <f t="shared" si="0"/>
         <v>5.25</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C10" s="2">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F10" s="3">
         <v>18</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="2">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E11" s="3">
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F11" s="3">
         <v>1.0900000000000001</v>
       </c>
-      <c r="F11" s="3">
+      <c r="G11" s="3">
         <f t="shared" si="0"/>
         <v>1.0900000000000001</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>111</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="2">
-        <v>1</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E12" s="3">
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F12" s="3">
         <v>0.57999999999999996</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <f t="shared" si="0"/>
         <v>0.57999999999999996</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C13" s="2">
-        <v>1</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="F13" s="3">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G13" s="3">
+        <f t="shared" si="0"/>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E13" s="3">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="F13" s="3">
-        <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="2">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F14" s="3">
         <v>8.23</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <f t="shared" si="0"/>
         <v>8.23</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C15" s="2">
-        <v>1</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E15" s="3">
+        <v>117</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15" s="3">
         <v>8.24</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <f t="shared" si="0"/>
         <v>8.24</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="L15" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="M15" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C16" s="2">
-        <v>1</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E16" s="3">
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F16" s="3">
         <v>2.0299999999999998</v>
       </c>
-      <c r="F16" s="3">
+      <c r="G16" s="3">
         <f t="shared" si="0"/>
         <v>2.0299999999999998</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="2">
-        <v>1</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E17" s="3">
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F17" s="3">
         <v>0.2</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="D18" s="2">
+        <v>3</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G18" s="3">
+        <f t="shared" si="0"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C18" s="2">
-        <v>3</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E18" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="F18" s="3">
-        <f t="shared" si="0"/>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="2">
+      <c r="D19" s="2">
         <v>3</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E19" s="3">
+      <c r="E19" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F19" s="3">
         <v>0.1</v>
       </c>
-      <c r="F19" s="3">
+      <c r="G19" s="3">
         <f t="shared" si="0"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>103</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="2">
+      <c r="D20" s="2">
         <v>4</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="E20" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F20" s="3">
         <v>0.1</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="I20" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="D21" s="2">
+        <v>2</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G21" s="3">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C21" s="2">
-        <v>2</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E21" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="F21" s="3">
-        <f t="shared" si="0"/>
-        <v>0.2</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C22" s="2">
-        <v>1</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="D22" s="2">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F22" s="3">
         <v>0.39</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <f t="shared" si="0"/>
         <v>0.39</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="I22" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>105</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C23" s="2">
-        <v>1</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E23" s="3">
+      <c r="D23" s="2">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F23" s="3">
         <v>0.41</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <f t="shared" si="0"/>
         <v>0.41</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="I23" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>100</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="2">
-        <v>1</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="D24" s="2">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F24" s="3">
         <v>0.26</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <f t="shared" si="0"/>
         <v>0.26</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="H24" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="I24" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="2">
+      <c r="D25" s="2">
         <v>4</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E25" s="3">
+      <c r="E25" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F25" s="3">
         <v>0.48</v>
       </c>
-      <c r="F25" s="3">
+      <c r="G25" s="3">
         <f t="shared" si="0"/>
         <v>1.92</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="I25" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C26" s="2">
-        <v>1</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E26" s="3">
+      <c r="D26" s="2">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F26" s="3">
         <v>3.58</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <f t="shared" si="0"/>
         <v>3.58</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="H26" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="I26" s="2" t="s">
+      <c r="J26" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="2">
-        <v>1</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E27" s="3">
+      <c r="D27" s="2">
+        <v>1</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F27" s="3">
         <v>60.76</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <f t="shared" si="0"/>
         <v>60.76</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="H27" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C28" s="2">
-        <v>1</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E28" s="3">
+      <c r="D28" s="2">
+        <v>1</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F28" s="3">
         <v>0.91</v>
       </c>
-      <c r="F28" s="3">
+      <c r="G28" s="3">
         <f t="shared" si="0"/>
         <v>0.91</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="H28" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="I28" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="2">
-        <v>1</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E29" s="3">
+      <c r="D29" s="2">
+        <v>1</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F29" s="3">
         <v>2.15</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <f t="shared" si="0"/>
         <v>2.15</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="H29" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="I29" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D30" s="2">
+        <v>1</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F30" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G30" s="3">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B30" s="2" t="s">
+    </row>
+    <row r="31" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="C30" s="2">
-        <v>1</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E30" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="F30" s="3">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C31" s="2">
-        <v>1</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E31" s="3">
+      <c r="D31" s="2">
+        <v>1</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F31" s="3">
         <v>0.13</v>
       </c>
-      <c r="F31" s="3">
+      <c r="G31" s="3">
         <f t="shared" si="0"/>
         <v>0.13</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="H31" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="I31" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="2">
+      <c r="D32" s="2">
         <v>9</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F32" s="3">
+        <v>7.39</v>
+      </c>
+      <c r="G32" s="3">
+        <f t="shared" si="0"/>
+        <v>66.509999999999991</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D33" s="2">
+        <v>2</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F33" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="G33" s="3">
+        <f t="shared" si="0"/>
+        <v>0.02</v>
+      </c>
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D34" s="2">
+        <v>2</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F34" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="G34" s="3">
+        <f t="shared" si="0"/>
+        <v>0.02</v>
+      </c>
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E32" s="3">
-        <v>7.39</v>
-      </c>
-      <c r="F32" s="3">
-        <f t="shared" si="0"/>
-        <v>66.509999999999991</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C33" s="2">
+      <c r="D35" s="2">
         <v>2</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E33" s="3">
+      <c r="E35" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F35" s="3">
         <v>0.01</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G35" s="3">
         <f t="shared" si="0"/>
         <v>0.02</v>
       </c>
-      <c r="G33" s="1"/>
-    </row>
-    <row r="34" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C34" s="2">
-        <v>2</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E34" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="F34" s="3">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
-      </c>
-      <c r="G34" s="1"/>
-    </row>
-    <row r="35" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="2" t="s">
+      <c r="H35" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C35" s="2">
-        <v>2</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E35" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="F35" s="3">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C36" s="2">
+      <c r="D36" s="2">
         <v>4</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E36" s="3">
+      <c r="E36" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F36" s="3">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="F36" s="3">
+      <c r="G36" s="3">
         <f t="shared" si="0"/>
         <v>0.29199999999999998</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="H36" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="37" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D37" s="2">
+        <v>1</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F37" s="3">
+        <v>2.68</v>
+      </c>
+      <c r="G37" s="3">
+        <f>D37*F37</f>
+        <v>2.68</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C37" s="2">
-        <v>1</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E37" s="3">
-        <v>2.68</v>
-      </c>
-      <c r="F37" s="3">
-        <f>C37*E37</f>
-        <v>2.68</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C38" s="2">
-        <v>1</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E38" s="3">
+      <c r="D38" s="2">
+        <v>1</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F38" s="3">
         <v>25</v>
       </c>
-      <c r="F38" s="3">
+      <c r="G38" s="3">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="H38" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="E39" s="4" t="s">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F39" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F39" s="4">
-        <f>SUM(F2:F38)</f>
+      <c r="G39" s="4">
+        <f>SUM(G2:G38)</f>
         <v>277.10200000000003</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{42481F3C-D77C-4D47-8482-158A61C0337E}"/>
-    <hyperlink ref="G4" r:id="rId2" display="https://www.amazon.com/Makerfire-Arduino-NRF24L01-Wireless-Transceiver/dp/B00O9O868G/ref=asc_df_B00O9O868G?mcid=dab308f0de3430dfa5c9f8399ca22b35&amp;hvocijid=9184541888213339040-B00O9O868G-&amp;hvexpln=73&amp;tag=hyprod-20&amp;linkCode=df0&amp;hvadid=721245378154&amp;hvpos=&amp;hvnetw=g&amp;hvrand=9184541888213339040&amp;hvpone=&amp;hvptwo=&amp;hvqmt=&amp;hvdev=c&amp;hvdvcmdl=&amp;hvlocint=&amp;hvlocphy=9198699&amp;hvtargid=pla-2281435177578&amp;psc=1" xr:uid="{89AEDB65-21E6-41D2-A940-81A81142AD5C}"/>
-    <hyperlink ref="G5" r:id="rId3" xr:uid="{E70F36E4-82C7-490A-965C-FBA0B568208C}"/>
-    <hyperlink ref="G6" r:id="rId4" display="https://www.amazon.com/Onyehn-Temperature-Humidity-Barometric-Pressure/dp/B07KR24P6P/ref=asc_df_B07KR24P6P?mcid=2faf80a473c33e3bb7b53dc75a65a9ac&amp;hvocijid=2199110702432476394-B07KR24P6P-&amp;hvexpln=73&amp;tag=hyprod-20&amp;linkCode=df0&amp;hvadid=721245378154&amp;hvpos=&amp;hvnetw=g&amp;hvrand=2199110702432476394&amp;hvpone=&amp;hvptwo=&amp;hvqmt=&amp;hvdev=c&amp;hvdvcmdl=&amp;hvlocint=&amp;hvlocphy=9198699&amp;hvtargid=pla-2281435177578&amp;psc=1" xr:uid="{04CEC65C-3665-4D25-B259-AF9E667F3BA6}"/>
-    <hyperlink ref="G8" r:id="rId5" xr:uid="{23E423E1-1EBE-4115-AE06-49032C41D232}"/>
-    <hyperlink ref="G9" r:id="rId6" display="https://www.sparkfun.com/ultrasonic-distance-sensor-hc-sr04.html" xr:uid="{F999829F-3DFC-4DBA-B819-1D673798FA55}"/>
-    <hyperlink ref="G10" r:id="rId7" display="https://zeeebattery.com/products/zeee-7-4v-60c-1500mah-2s-lipo-battery-deans-plug?variant=43953770299699&amp;country=US&amp;currency=USD&amp;utm_medium=product_sync&amp;utm_source=google&amp;utm_content=sag_organic&amp;utm_campaign=sag_organic&amp;gad_source=1&amp;gclid=CjwKCAjw7pO_BhAlEiwA4pMQvJInDAYww1F-RyBS_FKHJZs2q-GgKMjZj0IEfHsjSMYCjfxmAI9laxoCeRQQAvD_BwE" xr:uid="{BB8CB9D1-9310-4C54-A510-64D6DA058543}"/>
-    <hyperlink ref="G11" r:id="rId8" display="https://www.digikey.com/en/products/detail/jauch-quartz/CR1025/16399048" xr:uid="{17A29435-522E-4BB5-8364-3BC77FBEB1C4}"/>
-    <hyperlink ref="G12" r:id="rId9" display="https://www.digikey.com/en/products/detail/mpd-memory-protection-devices/bk-870/3829737" xr:uid="{27F9BEB5-8046-41B8-A401-6B801AA65292}"/>
-    <hyperlink ref="G17" r:id="rId10" display="https://www.digikey.com/en/products/detail/american-opto-plus-led/L314ED/13677700?s=N4IgTCBcDaIDIGYCMAWAogERAXQL5A" xr:uid="{EB1FB783-CD78-4F2E-ADAE-2EFC2E0C050D}"/>
-    <hyperlink ref="G20" r:id="rId11" xr:uid="{1CE23A94-3355-4CE3-BD99-944097BF2C76}"/>
-    <hyperlink ref="G25" r:id="rId12" display="https://www.digikey.com/en/products/detail/kemet/c1206s104k5racauto/10232834" xr:uid="{CDDFAE49-11BE-4283-9E44-D17951ACE335}"/>
-    <hyperlink ref="G26" r:id="rId13" display="https://www.digikey.com/en/products/detail/microchip-technology/mic5239-5-0ys-tr/2346595" xr:uid="{0FF0C8FA-B521-42B4-9637-4551CDF56AE0}"/>
-    <hyperlink ref="G28" r:id="rId14" display="https://www.digikey.com/en/products/detail/samtec-inc/ssa-104-w-t/1105908" xr:uid="{5CEFEAD0-E765-4C5C-8B17-4D481AAEE74F}"/>
-    <hyperlink ref="G14" r:id="rId15" xr:uid="{98CBDFFF-5BC0-4691-985C-193C55CD2A4F}"/>
-    <hyperlink ref="G16" r:id="rId16" xr:uid="{F40F3420-CF30-4700-92F3-040B50F37E84}"/>
-    <hyperlink ref="G23" r:id="rId17" xr:uid="{CF84383E-32DC-4F7A-8B1F-D5487EDC174E}"/>
-    <hyperlink ref="G24" r:id="rId18" xr:uid="{9AFC6348-0E57-4A67-A197-41D4FD45794D}"/>
-    <hyperlink ref="G3" r:id="rId19" xr:uid="{132AA37F-9E12-44EF-9546-36BDCE2F9F6B}"/>
-    <hyperlink ref="G32" r:id="rId20" xr:uid="{BECD5DE6-8852-4EA8-869E-7E18A46D5C74}"/>
-    <hyperlink ref="G31" r:id="rId21" display="https://www.digikey.com/en/products/detail/jst-sales-america-inc/B3B-XH-A/1651046?gad_source=1&amp;gad_campaignid=20470400566&amp;gbraid=0AAAAADrbLlgCz6Py2S0va5_igHe8YH5kP&amp;gclid=Cj0KCQjwuvrBBhDcARIsAKRrkjelT39dppIYbNMYGQDQKVRAcVAnRo2gDZvSJK6NkGomAkksSe1uUHcaAmLSEALw_wcB&amp;gclsrc=aw.ds" xr:uid="{9BDFB2BD-EFF6-4DEE-BBC3-2D01594D0DB0}"/>
-    <hyperlink ref="G22" r:id="rId22" xr:uid="{4FB5C311-0780-4C35-9E62-7B63EE0B1C7F}"/>
-    <hyperlink ref="G19" r:id="rId23" xr:uid="{11D1FB24-874A-4110-8E22-DCAAF354D69C}"/>
-    <hyperlink ref="H2" r:id="rId24" xr:uid="{BB65F326-57F6-0948-9C05-235DDBF32C5D}"/>
-    <hyperlink ref="I2" r:id="rId25" xr:uid="{85148DE2-C5FC-5645-B5BB-41BB837D9E5E}"/>
-    <hyperlink ref="H5" r:id="rId26" xr:uid="{41DE90D8-7589-0C4B-AD96-FF698779CC02}"/>
-    <hyperlink ref="I6" r:id="rId27" xr:uid="{50526146-D5B4-5C42-928A-1A4E698E0A66}"/>
-    <hyperlink ref="H10" r:id="rId28" display="https://www.ebay.com/itm/374993811392?chn=ps&amp;_trkparms=ispr%3D1&amp;amdata=enc%3A1tgCSJr3fRSKT8fAa1Y7Mgw25&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=374993811392&amp;targetid=2321110923741&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400684010&amp;mkgroupid=173029508068&amp;rlsatarget=pla-2321110923741&amp;abcId=9448486&amp;merchantid=6296724&amp;gad_source=1&amp;gad_campaignid=21400684010&amp;gbraid=0AAAAAD_QDh_duznfnFnLJIwhwQSUm0oBU&amp;gclid=EAIaIQobChMI3euy76jsjQMVFDQIBR3Brw42EAQYBSABEgL8OPD_BwE" xr:uid="{5370FA8F-6BA3-0A44-A70A-E9B0471E8594}"/>
-    <hyperlink ref="H19" r:id="rId29" xr:uid="{FAF305DA-B9D2-2244-A13B-6929AB49025C}"/>
-    <hyperlink ref="H26" r:id="rId30" xr:uid="{B99689F2-D490-2042-A4CC-3BA7CD9172AF}"/>
-    <hyperlink ref="G27" r:id="rId31" xr:uid="{1136733B-68A5-4A0B-995C-2A418A5AC777}"/>
-    <hyperlink ref="H3" r:id="rId32" display="https://www.ebay.com/itm/235081679206?chn=ps&amp;var=536091370095&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=536091370095_235081679206&amp;targetid=2295557532710&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400677539&amp;mkgroupid=173029508628&amp;rlsatarget=pla-2295557532710&amp;abcId=9448483&amp;merchantid=734150552&amp;gad_source=1&amp;gad_campaignid=21400677539&amp;gbraid=0AAAAAD_QDh9KZSet77KcrE8f9gL7cL_CG&amp;gclid=EAIaIQobChMIi8KGzaPsjQMVGEf_AR2yNzdrEAQYAyABEgL6F_D_BwE" xr:uid="{AD11255E-848C-4E6B-B235-2E174E495317}"/>
-    <hyperlink ref="G15" r:id="rId33" xr:uid="{DD127622-0F7B-0F49-8123-68EDBFB9D1FD}"/>
-    <hyperlink ref="H15" r:id="rId34" tooltip="https://www.staples.com/transcend-8gb-microsdhc-memory-card-class-10-ts8gusdhc10/product_IM1LK3226" xr:uid="{CD78FE6E-F962-024D-BECC-56B99B430391}"/>
-    <hyperlink ref="I15" r:id="rId35" tooltip="https://www.cdwg.com/product/transcend-flash-memory-card-8-gb-microsd/3181432?pfm=srh" xr:uid="{F7564EE8-2A81-B244-AEFD-6DA0DF39B5DC}"/>
-    <hyperlink ref="J15" r:id="rId36" tooltip="https://www.cdwg.com/product/kingston-industrial-flash-memory-card-8-gb-microsdhc-uhs-i/6669743?pfm=srh" xr:uid="{6EBC3D1F-2E28-7641-90A9-14D8B6437048}"/>
-    <hyperlink ref="G36" r:id="rId37" xr:uid="{AFFADB06-346C-4E3A-B07A-37D406DF404C}"/>
-    <hyperlink ref="G38" r:id="rId38" xr:uid="{EB0734B3-7C29-4D35-B394-905387802664}"/>
-    <hyperlink ref="G37" r:id="rId39" xr:uid="{26A48533-A061-40FE-A66E-723F0A8526D8}"/>
-    <hyperlink ref="G35" r:id="rId40" xr:uid="{327468E6-6FE8-4274-B476-C9C35280648B}"/>
-    <hyperlink ref="G30" r:id="rId41" display="https://www.digikey.com/en/products/detail/jst-sales-america-inc/B2B-XH-A/1651045?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20470400566&amp;gbraid=0AAAAADrbLljaCSzp9mL3BckOGUjmh-pLW&amp;gclid=CjwKCAiAoNbIBhB5EiwAZFbYGEhTlbpU8AtASh9T03rT2O-as-UbMvwFZowiONL1Xf91TSJaIz9zzBoCD-IQAvD_BwE" xr:uid="{A1578E18-966D-4A0B-89BB-AAA405790B24}"/>
-    <hyperlink ref="G7" r:id="rId42" xr:uid="{809BB693-6445-43CC-B4C1-47C121254BDE}"/>
-    <hyperlink ref="H7" r:id="rId43" xr:uid="{8E7D6AC4-E51D-48DC-AC39-840AA30DB295}"/>
-    <hyperlink ref="G21" r:id="rId44" xr:uid="{F2FBC813-F21B-4CA5-94D5-A1D3C7097891}"/>
-    <hyperlink ref="G13" r:id="rId45" xr:uid="{0C1E97B9-B29C-4292-84AE-9AEFCCB0C868}"/>
-    <hyperlink ref="G18" r:id="rId46" xr:uid="{51407470-A2C9-4C4E-89CA-FC24B70AF5A7}"/>
-    <hyperlink ref="H4" r:id="rId47" xr:uid="{1A2534D8-294F-4B39-89B1-8168C50C4225}"/>
-    <hyperlink ref="K6" r:id="rId48" xr:uid="{3B26DD18-290E-4BFE-BB80-46E0A92D8884}"/>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{42481F3C-D77C-4D47-8482-158A61C0337E}"/>
+    <hyperlink ref="H4" r:id="rId2" display="https://www.amazon.com/Makerfire-Arduino-NRF24L01-Wireless-Transceiver/dp/B00O9O868G/ref=asc_df_B00O9O868G?mcid=dab308f0de3430dfa5c9f8399ca22b35&amp;hvocijid=9184541888213339040-B00O9O868G-&amp;hvexpln=73&amp;tag=hyprod-20&amp;linkCode=df0&amp;hvadid=721245378154&amp;hvpos=&amp;hvnetw=g&amp;hvrand=9184541888213339040&amp;hvpone=&amp;hvptwo=&amp;hvqmt=&amp;hvdev=c&amp;hvdvcmdl=&amp;hvlocint=&amp;hvlocphy=9198699&amp;hvtargid=pla-2281435177578&amp;psc=1" xr:uid="{89AEDB65-21E6-41D2-A940-81A81142AD5C}"/>
+    <hyperlink ref="H5" r:id="rId3" xr:uid="{E70F36E4-82C7-490A-965C-FBA0B568208C}"/>
+    <hyperlink ref="I6" r:id="rId4" display="https://www.amazon.com/Onyehn-Temperature-Humidity-Barometric-Pressure/dp/B07KR24P6P/ref=asc_df_B07KR24P6P?mcid=2faf80a473c33e3bb7b53dc75a65a9ac&amp;hvocijid=2199110702432476394-B07KR24P6P-&amp;hvexpln=73&amp;tag=hyprod-20&amp;linkCode=df0&amp;hvadid=721245378154&amp;hvpos=&amp;hvnetw=g&amp;hvrand=2199110702432476394&amp;hvpone=&amp;hvptwo=&amp;hvqmt=&amp;hvdev=c&amp;hvdvcmdl=&amp;hvlocint=&amp;hvlocphy=9198699&amp;hvtargid=pla-2281435177578&amp;psc=1" xr:uid="{04CEC65C-3665-4D25-B259-AF9E667F3BA6}"/>
+    <hyperlink ref="H8" r:id="rId5" xr:uid="{23E423E1-1EBE-4115-AE06-49032C41D232}"/>
+    <hyperlink ref="H9" r:id="rId6" display="https://www.sparkfun.com/ultrasonic-distance-sensor-hc-sr04.html" xr:uid="{F999829F-3DFC-4DBA-B819-1D673798FA55}"/>
+    <hyperlink ref="H10" r:id="rId7" display="https://zeeebattery.com/products/zeee-7-4v-60c-1500mah-2s-lipo-battery-deans-plug?variant=43953770299699&amp;country=US&amp;currency=USD&amp;utm_medium=product_sync&amp;utm_source=google&amp;utm_content=sag_organic&amp;utm_campaign=sag_organic&amp;gad_source=1&amp;gclid=CjwKCAjw7pO_BhAlEiwA4pMQvJInDAYww1F-RyBS_FKHJZs2q-GgKMjZj0IEfHsjSMYCjfxmAI9laxoCeRQQAvD_BwE" xr:uid="{BB8CB9D1-9310-4C54-A510-64D6DA058543}"/>
+    <hyperlink ref="H11" r:id="rId8" display="https://www.digikey.com/en/products/detail/jauch-quartz/CR1025/16399048" xr:uid="{17A29435-522E-4BB5-8364-3BC77FBEB1C4}"/>
+    <hyperlink ref="H12" r:id="rId9" display="https://www.digikey.com/en/products/detail/mpd-memory-protection-devices/bk-870/3829737" xr:uid="{27F9BEB5-8046-41B8-A401-6B801AA65292}"/>
+    <hyperlink ref="H17" r:id="rId10" display="https://www.digikey.com/en/products/detail/american-opto-plus-led/L314ED/13677700?s=N4IgTCBcDaIDIGYCMAWAogERAXQL5A" xr:uid="{EB1FB783-CD78-4F2E-ADAE-2EFC2E0C050D}"/>
+    <hyperlink ref="H20" r:id="rId11" xr:uid="{1CE23A94-3355-4CE3-BD99-944097BF2C76}"/>
+    <hyperlink ref="H25" r:id="rId12" display="https://www.digikey.com/en/products/detail/kemet/c1206s104k5racauto/10232834" xr:uid="{CDDFAE49-11BE-4283-9E44-D17951ACE335}"/>
+    <hyperlink ref="H26" r:id="rId13" display="https://www.digikey.com/en/products/detail/microchip-technology/mic5239-5-0ys-tr/2346595" xr:uid="{0FF0C8FA-B521-42B4-9637-4551CDF56AE0}"/>
+    <hyperlink ref="H28" r:id="rId14" display="https://www.digikey.com/en/products/detail/samtec-inc/ssa-104-w-t/1105908" xr:uid="{5CEFEAD0-E765-4C5C-8B17-4D481AAEE74F}"/>
+    <hyperlink ref="H14" r:id="rId15" xr:uid="{98CBDFFF-5BC0-4691-985C-193C55CD2A4F}"/>
+    <hyperlink ref="H16" r:id="rId16" xr:uid="{F40F3420-CF30-4700-92F3-040B50F37E84}"/>
+    <hyperlink ref="H23" r:id="rId17" xr:uid="{CF84383E-32DC-4F7A-8B1F-D5487EDC174E}"/>
+    <hyperlink ref="H24" r:id="rId18" xr:uid="{9AFC6348-0E57-4A67-A197-41D4FD45794D}"/>
+    <hyperlink ref="H3" r:id="rId19" xr:uid="{132AA37F-9E12-44EF-9546-36BDCE2F9F6B}"/>
+    <hyperlink ref="H32" r:id="rId20" xr:uid="{BECD5DE6-8852-4EA8-869E-7E18A46D5C74}"/>
+    <hyperlink ref="H31" r:id="rId21" display="https://www.digikey.com/en/products/detail/jst-sales-america-inc/B3B-XH-A/1651046?gad_source=1&amp;gad_campaignid=20470400566&amp;gbraid=0AAAAADrbLlgCz6Py2S0va5_igHe8YH5kP&amp;gclid=Cj0KCQjwuvrBBhDcARIsAKRrkjelT39dppIYbNMYGQDQKVRAcVAnRo2gDZvSJK6NkGomAkksSe1uUHcaAmLSEALw_wcB&amp;gclsrc=aw.ds" xr:uid="{9BDFB2BD-EFF6-4DEE-BBC3-2D01594D0DB0}"/>
+    <hyperlink ref="H22" r:id="rId22" xr:uid="{4FB5C311-0780-4C35-9E62-7B63EE0B1C7F}"/>
+    <hyperlink ref="H19" r:id="rId23" xr:uid="{11D1FB24-874A-4110-8E22-DCAAF354D69C}"/>
+    <hyperlink ref="I2" r:id="rId24" xr:uid="{BB65F326-57F6-0948-9C05-235DDBF32C5D}"/>
+    <hyperlink ref="J2" r:id="rId25" xr:uid="{85148DE2-C5FC-5645-B5BB-41BB837D9E5E}"/>
+    <hyperlink ref="I5" r:id="rId26" xr:uid="{41DE90D8-7589-0C4B-AD96-FF698779CC02}"/>
+    <hyperlink ref="K6" r:id="rId27" xr:uid="{50526146-D5B4-5C42-928A-1A4E698E0A66}"/>
+    <hyperlink ref="I10" r:id="rId28" display="https://www.ebay.com/itm/374993811392?chn=ps&amp;_trkparms=ispr%3D1&amp;amdata=enc%3A1tgCSJr3fRSKT8fAa1Y7Mgw25&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=374993811392&amp;targetid=2321110923741&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400684010&amp;mkgroupid=173029508068&amp;rlsatarget=pla-2321110923741&amp;abcId=9448486&amp;merchantid=6296724&amp;gad_source=1&amp;gad_campaignid=21400684010&amp;gbraid=0AAAAAD_QDh_duznfnFnLJIwhwQSUm0oBU&amp;gclid=EAIaIQobChMI3euy76jsjQMVFDQIBR3Brw42EAQYBSABEgL8OPD_BwE" xr:uid="{5370FA8F-6BA3-0A44-A70A-E9B0471E8594}"/>
+    <hyperlink ref="I19" r:id="rId29" xr:uid="{FAF305DA-B9D2-2244-A13B-6929AB49025C}"/>
+    <hyperlink ref="I26" r:id="rId30" xr:uid="{B99689F2-D490-2042-A4CC-3BA7CD9172AF}"/>
+    <hyperlink ref="H27" r:id="rId31" xr:uid="{1136733B-68A5-4A0B-995C-2A418A5AC777}"/>
+    <hyperlink ref="I3" r:id="rId32" display="https://www.ebay.com/itm/235081679206?chn=ps&amp;var=536091370095&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=536091370095_235081679206&amp;targetid=2295557532710&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400677539&amp;mkgroupid=173029508628&amp;rlsatarget=pla-2295557532710&amp;abcId=9448483&amp;merchantid=734150552&amp;gad_source=1&amp;gad_campaignid=21400677539&amp;gbraid=0AAAAAD_QDh9KZSet77KcrE8f9gL7cL_CG&amp;gclid=EAIaIQobChMIi8KGzaPsjQMVGEf_AR2yNzdrEAQYAyABEgL6F_D_BwE" xr:uid="{AD11255E-848C-4E6B-B235-2E174E495317}"/>
+    <hyperlink ref="H15" r:id="rId33" xr:uid="{DD127622-0F7B-0F49-8123-68EDBFB9D1FD}"/>
+    <hyperlink ref="I15" r:id="rId34" tooltip="https://www.staples.com/transcend-8gb-microsdhc-memory-card-class-10-ts8gusdhc10/product_IM1LK3226" xr:uid="{CD78FE6E-F962-024D-BECC-56B99B430391}"/>
+    <hyperlink ref="J15" r:id="rId35" tooltip="https://www.cdwg.com/product/transcend-flash-memory-card-8-gb-microsd/3181432?pfm=srh" xr:uid="{F7564EE8-2A81-B244-AEFD-6DA0DF39B5DC}"/>
+    <hyperlink ref="K15" r:id="rId36" tooltip="https://www.cdwg.com/product/kingston-industrial-flash-memory-card-8-gb-microsdhc-uhs-i/6669743?pfm=srh" xr:uid="{6EBC3D1F-2E28-7641-90A9-14D8B6437048}"/>
+    <hyperlink ref="H36" r:id="rId37" xr:uid="{AFFADB06-346C-4E3A-B07A-37D406DF404C}"/>
+    <hyperlink ref="H38" r:id="rId38" xr:uid="{EB0734B3-7C29-4D35-B394-905387802664}"/>
+    <hyperlink ref="H37" r:id="rId39" xr:uid="{26A48533-A061-40FE-A66E-723F0A8526D8}"/>
+    <hyperlink ref="H35" r:id="rId40" xr:uid="{327468E6-6FE8-4274-B476-C9C35280648B}"/>
+    <hyperlink ref="H30" r:id="rId41" display="https://www.digikey.com/en/products/detail/jst-sales-america-inc/B2B-XH-A/1651045?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20470400566&amp;gbraid=0AAAAADrbLljaCSzp9mL3BckOGUjmh-pLW&amp;gclid=CjwKCAiAoNbIBhB5EiwAZFbYGEhTlbpU8AtASh9T03rT2O-as-UbMvwFZowiONL1Xf91TSJaIz9zzBoCD-IQAvD_BwE" xr:uid="{A1578E18-966D-4A0B-89BB-AAA405790B24}"/>
+    <hyperlink ref="H7" r:id="rId42" xr:uid="{809BB693-6445-43CC-B4C1-47C121254BDE}"/>
+    <hyperlink ref="I7" r:id="rId43" xr:uid="{8E7D6AC4-E51D-48DC-AC39-840AA30DB295}"/>
+    <hyperlink ref="H21" r:id="rId44" xr:uid="{F2FBC813-F21B-4CA5-94D5-A1D3C7097891}"/>
+    <hyperlink ref="H13" r:id="rId45" xr:uid="{0C1E97B9-B29C-4292-84AE-9AEFCCB0C868}"/>
+    <hyperlink ref="H18" r:id="rId46" xr:uid="{51407470-A2C9-4C4E-89CA-FC24B70AF5A7}"/>
+    <hyperlink ref="I4" r:id="rId47" xr:uid="{1A2534D8-294F-4B39-89B1-8168C50C4225}"/>
+    <hyperlink ref="L6" r:id="rId48" xr:uid="{3B26DD18-290E-4BFE-BB80-46E0A92D8884}"/>
+    <hyperlink ref="J6" r:id="rId49" display="https://www.ebay.com/itm/223602242983?chn=ps&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=223602242983&amp;targetid=2295557532710&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400677539&amp;mkgroupid=173029508628&amp;rlsatarget=pla-2295557532710&amp;abcId=9448483&amp;merchantid=108461346&amp;gad_source=4&amp;gad_campaignid=21400677539&amp;gbraid=0AAAAAD_QDh9zBpIZmq8atlokvhUYT34hx&amp;gclid=EAIaIQobChMIyYbmlabsjQMVBjUIBR1KhTUNEAQYECABEgIh5fD_BwE" xr:uid="{8537022B-3B72-40E4-A752-C847F511BEE6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId49"/>
+  <pageSetup orientation="portrait" r:id="rId50"/>
 </worksheet>
 </file>
--- a/system_design/Georgetown/V0.5.2/bill_of_materials.xlsx
+++ b/system_design/Georgetown/V0.5.2/bill_of_materials.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\SWaP-Constrained-UAV-deployable-Water-Level-Sensor\system_design\Georgetown\V0.5.2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\UAV-Deployable-Stage-Height-Sensor\system_design\Georgetown\V0.5.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03FB38C-2BB2-4F7F-8258-5EC3F0FCDEF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91EA05C-203A-40B6-9D74-283D57AF09F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="28680" yWindow="-150" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="149">
   <si>
     <t>Arduino Nano</t>
   </si>
@@ -239,9 +239,6 @@
     <t>https://www.ebay.com/itm/133891769676?chn=ps&amp;mkevt=1&amp;mkcid=28&amp;google_free_listing_action=view_item&amp;srsltid=AfmBOoq4Q1DZuqzeXULhra-FvrHzA-CnA0tD2iHCO95TTtg9XNd3Ut4sVOs&amp;com_cvv=8fb3d522dc163aeadb66e08cd7450cbbdddc64c6cf2e8891f6d48747c6d56d2c</t>
   </si>
   <si>
-    <t>https://business.walmart.com/ip/Gigastone-8GB-Micro-SD-Card-FHD-Video-UHS-I-U1-Class-10-Surveillance-Security-Action-Cameras-Drone-Dash-Cams-5-Pack-5x8GB-GS-2IN1C1008GBX5-B/581920075</t>
-  </si>
-  <si>
     <t>https://www.mouser.com/ProductDetail/Wurth-Elektronik/450301014042?qs=wr8lucFkNMW0uepaR4R%2Fww%3D%3D&amp;mgh=1&amp;utm_id=22019447991&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_marketing_tactic=amercorp&amp;gad_source=1&amp;gad_campaignid=22019464944&amp;gbraid=0AAAAADn_wf3z6_iEM3qu9larZZD8yoLEt&amp;gclid=EAIaIQobChMI3veKsazsjQMVJ0X_AR3ueCPcEAQYBCABEgJYf_D_BwE</t>
   </si>
   <si>
@@ -284,21 +281,6 @@
     <t>https://www.ebay.com/itm/135516167050?_skw=B3B-XH-A&amp;itmmeta=01JXJN27KW3SV3ZA95H65390XD&amp;hash=item1f8d649b8a:g:2rIAAOSwhWlnlDUD&amp;itmprp=enc%3AAQAKAAAAwFkggFvd1GGDu0w3yXCmi1cVMih7yC%2FWve52RdwhMAlOgWsL1OoLM4xoBnc%2B7VbJxO7%2Fl5Q2%2B19FN%2Ffcf4Nh7uGxttthvmZ%2BZODMfmWlr3tqV99qA67ltarFMPt0GZ5Q0hGKwVEs3cWQzRsgzIEMfPrKwt%2FXoqS0kqv8N3acTaphgw--%2B1HloQZc3MjBQEeC3t1OszQttaoyVtLG7P0WoB7S3sUOfGn60RdftLEZV%2BMqhhcdr8JYIK2PYQMDH3SJaA%3D%3D%7Ctkp%3ABk9SR5b6iNXsZQ</t>
   </si>
   <si>
-    <t>https://www.staples.com/centon-micro-8gb-sdhc-memory-card-uhs1-5-pack-s1-msdhu1-8g-5-b/product_24298979?locupd=y</t>
-  </si>
-  <si>
-    <t>https://www.staples.com/transcend-8gb-microsdhc-memory-card-class-10-ts8gusdhc10/product_IM1LK3226</t>
-  </si>
-  <si>
-    <t>https://www.cdwg.com/product/transcend-flash-memory-card-8-gb-microsd/3181432?pfm=srh</t>
-  </si>
-  <si>
-    <t>https://www.cdwg.com/product/kingston-industrial-flash-memory-card-8-gb-microsdhc-uhs-i/6669743?pfm=srh</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/Gigastone-10-Pack-Surveillance-Security-Action/dp/B0876H387X/ref=asc_df_B0876H387X?mcid=a36b7487c2ef3bf38be475383d962644&amp;hvocijid=8673258576435803325-B0876H387X-&amp;hvexpln=73&amp;tag=hyprod-20&amp;linkCode=df0&amp;hvadid=721245378154&amp;hvpos=&amp;hvnetw=g&amp;hvrand=8673258576435803325&amp;hvpone=&amp;hvptwo=&amp;hvqmt=&amp;hvdev=c&amp;hvdvcmdl=&amp;hvlocint=&amp;hvlocphy=9198699&amp;hvtargid=pla-2281435181978&amp;th=1</t>
-  </si>
-  <si>
     <t>Vendor 4</t>
   </si>
   <si>
@@ -389,9 +371,6 @@
     <t>SSA-104-W-T,  4 pin connector</t>
   </si>
   <si>
-    <t xml:space="preserve"> 8GB Micro SD Card</t>
-  </si>
-  <si>
     <t>D2 (LED)</t>
   </si>
   <si>
@@ -498,6 +477,12 @@
   </si>
   <si>
     <t>https://www.aliexpress.us/item/3256807913818826.html?src=google&amp;src=google&amp;albch=shopping&amp;acnt=708-803-3821&amp;isdl=y&amp;slnk=&amp;plac=&amp;mtctp=&amp;albbt=Google_7_shopping&amp;aff_platform=google&amp;aff_short_key=UneMJZVf&amp;gclsrc=aw.ds&amp;albagn=888888&amp;ds_e_adid=&amp;ds_e_matchtype=&amp;ds_e_device=c&amp;ds_e_network=x&amp;ds_e_product_group_id=&amp;ds_e_product_id=en3256807913818826&amp;ds_e_product_merchant_id=5343266820&amp;ds_e_product_country=US&amp;ds_e_product_language=en&amp;ds_e_product_channel=online&amp;ds_e_product_store_id=&amp;ds_url_v=2&amp;albcp=19558607238&amp;albag=&amp;isSmbAutoCall=false&amp;needSmbHouyi=false&amp;gad_source=1&amp;gad_campaignid=19566915268&amp;gbraid=0AAAAAD6I-hE1DxC2gZnFOXHh1kEusbMcy&amp;gclid=CjwKCAjwsfzSBhB5EiwAOGyqSRU193oQHDmqvw43tZsck5IFRgE9x0LpmqXCbfoW00kjTDmN2fMHGhoCCf0QAvD_BwE&amp;gatewayAdapt=glo2usa</t>
+  </si>
+  <si>
+    <t>16 GB Micro SD Card</t>
+  </si>
+  <si>
+    <t>https://www.staplesadvantage.com/centon-16gb-microsd-memory-card-with-adapter-class-10-s1msdhu116g/product_1587077_1587077-4400034214</t>
   </si>
 </sst>
 </file>
@@ -945,19 +930,19 @@
   <sheetData>
     <row r="1" spans="1:13" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>17</v>
@@ -975,13 +960,13 @@
         <v>52</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -995,7 +980,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F2" s="3">
         <v>25.7</v>
@@ -1016,16 +1001,16 @@
     </row>
     <row r="3" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F3" s="3">
         <v>2.52</v>
@@ -1052,7 +1037,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F4" s="3">
         <v>1.4</v>
@@ -1073,16 +1058,16 @@
     </row>
     <row r="5" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F5" s="3">
         <v>11.96</v>
@@ -1100,16 +1085,16 @@
     </row>
     <row r="6" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F6" s="3">
         <v>5.26</v>
@@ -1119,7 +1104,7 @@
         <v>5.26</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>21</v>
@@ -1131,21 +1116,21 @@
         <v>60</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F7" s="3">
         <v>4.95</v>
@@ -1155,10 +1140,10 @@
         <v>4.95</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1172,7 +1157,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F8" s="3">
         <v>15.2</v>
@@ -1196,7 +1181,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F9" s="3">
         <v>5.25</v>
@@ -1220,13 +1205,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F10" s="3">
         <v>18</v>
@@ -1256,7 +1241,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F11" s="3">
         <v>1.0900000000000001</v>
@@ -1274,7 +1259,7 @@
     </row>
     <row r="12" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>9</v>
@@ -1283,7 +1268,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F12" s="3">
         <v>0.57999999999999996</v>
@@ -1301,16 +1286,16 @@
     </row>
     <row r="13" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D13" s="2">
         <v>1</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="F13" s="3">
         <v>0.14000000000000001</v>
@@ -1320,12 +1305,12 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>10</v>
@@ -1334,7 +1319,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F14" s="3">
         <v>8.23</v>
@@ -1352,52 +1337,40 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F15" s="3">
-        <v>8.24</v>
+        <v>6.47</v>
       </c>
       <c r="G15" s="3">
         <f t="shared" si="0"/>
-        <v>8.24</v>
+        <v>6.47</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>86</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
     </row>
     <row r="16" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D16" s="2">
         <v>1</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F16" s="3">
         <v>2.0299999999999998</v>
@@ -1410,21 +1383,21 @@
         <v>45</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D17" s="2">
         <v>1</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F17" s="3">
         <v>0.2</v>
@@ -1437,21 +1410,21 @@
         <v>28</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F18" s="3">
         <v>0.1</v>
@@ -1461,12 +1434,12 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>48</v>
@@ -1475,7 +1448,7 @@
         <v>3</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F19" s="3">
         <v>0.1</v>
@@ -1488,12 +1461,12 @@
         <v>50</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>47</v>
@@ -1502,7 +1475,7 @@
         <v>4</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F20" s="3">
         <v>0.1</v>
@@ -1515,21 +1488,21 @@
         <v>49</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D21" s="2">
         <v>2</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F21" s="3">
         <v>0.1</v>
@@ -1539,21 +1512,21 @@
         <v>0.2</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D22" s="2">
         <v>1</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F22" s="3">
         <v>0.39</v>
@@ -1566,21 +1539,21 @@
         <v>43</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D23" s="2">
         <v>1</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F23" s="3">
         <v>0.41</v>
@@ -1593,21 +1566,21 @@
         <v>34</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D24" s="2">
         <v>1</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F24" s="3">
         <v>0.26</v>
@@ -1620,12 +1593,12 @@
         <v>35</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>33</v>
@@ -1634,7 +1607,7 @@
         <v>4</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F25" s="3">
         <v>0.48</v>
@@ -1647,21 +1620,21 @@
         <v>29</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D26" s="2">
         <v>1</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F26" s="3">
         <v>3.58</v>
@@ -1674,10 +1647,10 @@
         <v>30</v>
       </c>
       <c r="I26" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J26" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1691,7 +1664,7 @@
         <v>1</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F27" s="3">
         <v>60.76</v>
@@ -1701,7 +1674,7 @@
         <v>60.76</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1709,13 +1682,13 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D28" s="2">
         <v>1</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F28" s="3">
         <v>0.91</v>
@@ -1728,12 +1701,12 @@
         <v>31</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>38</v>
@@ -1742,7 +1715,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F29" s="3">
         <v>2.15</v>
@@ -1755,21 +1728,21 @@
         <v>37</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F30" s="3">
         <v>0.1</v>
@@ -1779,21 +1752,21 @@
         <v>0.1</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F31" s="3">
         <v>0.13</v>
@@ -1806,7 +1779,7 @@
         <v>42</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1820,7 +1793,7 @@
         <v>9</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F32" s="3">
         <v>7.39</v>
@@ -1835,13 +1808,13 @@
     </row>
     <row r="33" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D33" s="2">
         <v>2</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F33" s="3">
         <v>0.01</v>
@@ -1854,13 +1827,13 @@
     </row>
     <row r="34" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D34" s="2">
         <v>2</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F34" s="3">
         <v>0.01</v>
@@ -1873,13 +1846,13 @@
     </row>
     <row r="35" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D35" s="2">
         <v>2</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F35" s="3">
         <v>0.01</v>
@@ -1889,18 +1862,18 @@
         <v>0.02</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D36" s="2">
         <v>4</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F36" s="3">
         <v>7.2999999999999995E-2</v>
@@ -1910,21 +1883,21 @@
         <v>0.29199999999999998</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D37" s="2">
         <v>1</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F37" s="3">
         <v>2.68</v>
@@ -1934,21 +1907,21 @@
         <v>2.68</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D38" s="2">
         <v>1</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F38" s="3">
         <v>25</v>
@@ -1958,7 +1931,7 @@
         <v>25</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -1967,7 +1940,7 @@
       </c>
       <c r="G39" s="4">
         <f>SUM(G2:G38)</f>
-        <v>277.10200000000003</v>
+        <v>275.33199999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2004,25 +1977,22 @@
     <hyperlink ref="I26" r:id="rId30" xr:uid="{B99689F2-D490-2042-A4CC-3BA7CD9172AF}"/>
     <hyperlink ref="H27" r:id="rId31" xr:uid="{1136733B-68A5-4A0B-995C-2A418A5AC777}"/>
     <hyperlink ref="I3" r:id="rId32" display="https://www.ebay.com/itm/235081679206?chn=ps&amp;var=536091370095&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=536091370095_235081679206&amp;targetid=2295557532710&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400677539&amp;mkgroupid=173029508628&amp;rlsatarget=pla-2295557532710&amp;abcId=9448483&amp;merchantid=734150552&amp;gad_source=1&amp;gad_campaignid=21400677539&amp;gbraid=0AAAAAD_QDh9KZSet77KcrE8f9gL7cL_CG&amp;gclid=EAIaIQobChMIi8KGzaPsjQMVGEf_AR2yNzdrEAQYAyABEgL6F_D_BwE" xr:uid="{AD11255E-848C-4E6B-B235-2E174E495317}"/>
-    <hyperlink ref="H15" r:id="rId33" xr:uid="{DD127622-0F7B-0F49-8123-68EDBFB9D1FD}"/>
-    <hyperlink ref="I15" r:id="rId34" tooltip="https://www.staples.com/transcend-8gb-microsdhc-memory-card-class-10-ts8gusdhc10/product_IM1LK3226" xr:uid="{CD78FE6E-F962-024D-BECC-56B99B430391}"/>
-    <hyperlink ref="J15" r:id="rId35" tooltip="https://www.cdwg.com/product/transcend-flash-memory-card-8-gb-microsd/3181432?pfm=srh" xr:uid="{F7564EE8-2A81-B244-AEFD-6DA0DF39B5DC}"/>
-    <hyperlink ref="K15" r:id="rId36" tooltip="https://www.cdwg.com/product/kingston-industrial-flash-memory-card-8-gb-microsdhc-uhs-i/6669743?pfm=srh" xr:uid="{6EBC3D1F-2E28-7641-90A9-14D8B6437048}"/>
-    <hyperlink ref="H36" r:id="rId37" xr:uid="{AFFADB06-346C-4E3A-B07A-37D406DF404C}"/>
-    <hyperlink ref="H38" r:id="rId38" xr:uid="{EB0734B3-7C29-4D35-B394-905387802664}"/>
-    <hyperlink ref="H37" r:id="rId39" xr:uid="{26A48533-A061-40FE-A66E-723F0A8526D8}"/>
-    <hyperlink ref="H35" r:id="rId40" xr:uid="{327468E6-6FE8-4274-B476-C9C35280648B}"/>
-    <hyperlink ref="H30" r:id="rId41" display="https://www.digikey.com/en/products/detail/jst-sales-america-inc/B2B-XH-A/1651045?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20470400566&amp;gbraid=0AAAAADrbLljaCSzp9mL3BckOGUjmh-pLW&amp;gclid=CjwKCAiAoNbIBhB5EiwAZFbYGEhTlbpU8AtASh9T03rT2O-as-UbMvwFZowiONL1Xf91TSJaIz9zzBoCD-IQAvD_BwE" xr:uid="{A1578E18-966D-4A0B-89BB-AAA405790B24}"/>
-    <hyperlink ref="H7" r:id="rId42" xr:uid="{809BB693-6445-43CC-B4C1-47C121254BDE}"/>
-    <hyperlink ref="I7" r:id="rId43" xr:uid="{8E7D6AC4-E51D-48DC-AC39-840AA30DB295}"/>
-    <hyperlink ref="H21" r:id="rId44" xr:uid="{F2FBC813-F21B-4CA5-94D5-A1D3C7097891}"/>
-    <hyperlink ref="H13" r:id="rId45" xr:uid="{0C1E97B9-B29C-4292-84AE-9AEFCCB0C868}"/>
-    <hyperlink ref="H18" r:id="rId46" xr:uid="{51407470-A2C9-4C4E-89CA-FC24B70AF5A7}"/>
-    <hyperlink ref="I4" r:id="rId47" xr:uid="{1A2534D8-294F-4B39-89B1-8168C50C4225}"/>
-    <hyperlink ref="L6" r:id="rId48" xr:uid="{3B26DD18-290E-4BFE-BB80-46E0A92D8884}"/>
-    <hyperlink ref="J6" r:id="rId49" display="https://www.ebay.com/itm/223602242983?chn=ps&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=223602242983&amp;targetid=2295557532710&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400677539&amp;mkgroupid=173029508628&amp;rlsatarget=pla-2295557532710&amp;abcId=9448483&amp;merchantid=108461346&amp;gad_source=4&amp;gad_campaignid=21400677539&amp;gbraid=0AAAAAD_QDh9zBpIZmq8atlokvhUYT34hx&amp;gclid=EAIaIQobChMIyYbmlabsjQMVBjUIBR1KhTUNEAQYECABEgIh5fD_BwE" xr:uid="{8537022B-3B72-40E4-A752-C847F511BEE6}"/>
+    <hyperlink ref="H36" r:id="rId33" xr:uid="{AFFADB06-346C-4E3A-B07A-37D406DF404C}"/>
+    <hyperlink ref="H38" r:id="rId34" xr:uid="{EB0734B3-7C29-4D35-B394-905387802664}"/>
+    <hyperlink ref="H37" r:id="rId35" xr:uid="{26A48533-A061-40FE-A66E-723F0A8526D8}"/>
+    <hyperlink ref="H35" r:id="rId36" xr:uid="{327468E6-6FE8-4274-B476-C9C35280648B}"/>
+    <hyperlink ref="H30" r:id="rId37" display="https://www.digikey.com/en/products/detail/jst-sales-america-inc/B2B-XH-A/1651045?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20470400566&amp;gbraid=0AAAAADrbLljaCSzp9mL3BckOGUjmh-pLW&amp;gclid=CjwKCAiAoNbIBhB5EiwAZFbYGEhTlbpU8AtASh9T03rT2O-as-UbMvwFZowiONL1Xf91TSJaIz9zzBoCD-IQAvD_BwE" xr:uid="{A1578E18-966D-4A0B-89BB-AAA405790B24}"/>
+    <hyperlink ref="H7" r:id="rId38" xr:uid="{809BB693-6445-43CC-B4C1-47C121254BDE}"/>
+    <hyperlink ref="I7" r:id="rId39" xr:uid="{8E7D6AC4-E51D-48DC-AC39-840AA30DB295}"/>
+    <hyperlink ref="H21" r:id="rId40" xr:uid="{F2FBC813-F21B-4CA5-94D5-A1D3C7097891}"/>
+    <hyperlink ref="H13" r:id="rId41" xr:uid="{0C1E97B9-B29C-4292-84AE-9AEFCCB0C868}"/>
+    <hyperlink ref="H18" r:id="rId42" xr:uid="{51407470-A2C9-4C4E-89CA-FC24B70AF5A7}"/>
+    <hyperlink ref="I4" r:id="rId43" xr:uid="{1A2534D8-294F-4B39-89B1-8168C50C4225}"/>
+    <hyperlink ref="L6" r:id="rId44" xr:uid="{3B26DD18-290E-4BFE-BB80-46E0A92D8884}"/>
+    <hyperlink ref="J6" r:id="rId45" display="https://www.ebay.com/itm/223602242983?chn=ps&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=223602242983&amp;targetid=2295557532710&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400677539&amp;mkgroupid=173029508628&amp;rlsatarget=pla-2295557532710&amp;abcId=9448483&amp;merchantid=108461346&amp;gad_source=4&amp;gad_campaignid=21400677539&amp;gbraid=0AAAAAD_QDh9zBpIZmq8atlokvhUYT34hx&amp;gclid=EAIaIQobChMIyYbmlabsjQMVBjUIBR1KhTUNEAQYECABEgIh5fD_BwE" xr:uid="{8537022B-3B72-40E4-A752-C847F511BEE6}"/>
+    <hyperlink ref="H15" r:id="rId46" xr:uid="{A6F3856D-694D-4B77-926C-45B40107F580}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId50"/>
+  <pageSetup orientation="portrait" r:id="rId47"/>
 </worksheet>
 </file>
--- a/system_design/Georgetown/V0.5.2/bill_of_materials.xlsx
+++ b/system_design/Georgetown/V0.5.2/bill_of_materials.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\SWaP-Constrained-UAV-deployable-Water-Level-Sensor\system_design\Georgetown\V0.5.2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/asifuzzaman_sc_edu/Documents/Github Repos/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5.2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03FB38C-2BB2-4F7F-8258-5EC3F0FCDEF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{D03FB38C-2BB2-4F7F-8258-5EC3F0FCDEF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A280CD80-4589-40BA-AB22-9C2530583FA7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="153">
   <si>
     <t>Arduino Nano</t>
   </si>
@@ -227,12 +227,6 @@
     <t>https://www.ebay.com/itm/192312930293?chn=ps&amp;mkevt=1&amp;mkcid=28&amp;google_free_listing_action=view_item&amp;srsltid=AfmBOoqR3Oigp1kS_GZXXLiCTeaArw929kUvWVy0fyYHeb0FzpclMz12k3M</t>
   </si>
   <si>
-    <t>https://www.ebay.com/itm/374993811392?chn=ps&amp;_trkparms=ispr%3D1&amp;amdata=enc%3A1tgCSJr3fRSKT8fAa1Y7Mgw25&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=374993811392&amp;targetid=2321110923741&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400684010&amp;mkgroupid=173029508068&amp;rlsatarget=pla-2321110923741&amp;abcId=9448486&amp;merchantid=6296724&amp;gad_source=1&amp;gad_campaignid=21400684010&amp;gbraid=0AAAAAD_QDh_duznfnFnLJIwhwQSUm0oBU&amp;gclid=EAIaIQobChMI3euy76jsjQMVFDQIBR3Brw42EAQYBSABEgL8OPD_BwE</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/sparkfun-electronics/11855/5271297?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20243136172&amp;gbraid=0AAAAADrbLli4_Ap0H678W2amsXvkFFD8z&amp;gclid=EAIaIQobChMI3euy76jsjQMVFDQIBR3Brw42EAQYAiABEgIY4fD_BwE</t>
-  </si>
-  <si>
     <t>https://www.ebay.com/itm/365610739537?chn=ps&amp;mkevt=1&amp;mkcid=28&amp;google_free_listing_action=view_item&amp;srsltid=AfmBOoporY_55WDnNvV2pejIbeRgMhPaBkQWl3ds383-qDG6cI2P8OGNJXw&amp;com_cvv=8fb3d522dc163aeadb66e08cd7450cbbdddc64c6cf2e8891f6d48747c6d56d2c</t>
   </si>
   <si>
@@ -368,9 +362,6 @@
     <t xml:space="preserve">U4 (BME280) </t>
   </si>
   <si>
-    <t xml:space="preserve"> BME280 environmental sensor</t>
-  </si>
-  <si>
     <t>BT1  (coin cell holder)</t>
   </si>
   <si>
@@ -497,7 +488,13 @@
     <t>manufacturer part number</t>
   </si>
   <si>
-    <t>https://www.aliexpress.us/item/3256807913818826.html?src=google&amp;src=google&amp;albch=shopping&amp;acnt=708-803-3821&amp;isdl=y&amp;slnk=&amp;plac=&amp;mtctp=&amp;albbt=Google_7_shopping&amp;aff_platform=google&amp;aff_short_key=UneMJZVf&amp;gclsrc=aw.ds&amp;albagn=888888&amp;ds_e_adid=&amp;ds_e_matchtype=&amp;ds_e_device=c&amp;ds_e_network=x&amp;ds_e_product_group_id=&amp;ds_e_product_id=en3256807913818826&amp;ds_e_product_merchant_id=5343266820&amp;ds_e_product_country=US&amp;ds_e_product_language=en&amp;ds_e_product_channel=online&amp;ds_e_product_store_id=&amp;ds_url_v=2&amp;albcp=19558607238&amp;albag=&amp;isSmbAutoCall=false&amp;needSmbHouyi=false&amp;gad_source=1&amp;gad_campaignid=19566915268&amp;gbraid=0AAAAAD6I-hE1DxC2gZnFOXHh1kEusbMcy&amp;gclid=CjwKCAjwsfzSBhB5EiwAOGyqSRU193oQHDmqvw43tZsck5IFRgE9x0LpmqXCbfoW00kjTDmN2fMHGhoCCf0QAvD_BwE&amp;gatewayAdapt=glo2usa</t>
+    <t>https://www.ebay.com/itm/383205406858</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/327147846952?_skw=BME280+5+V&amp;itmmeta=01KZVT1RTW26G1WWC3Y7NSNY2T&amp;hash=item4c2b87fd28:g:P1MAAeSwcWdp~jCK&amp;itmprp=enc%3AAQALAAAA8GfYFPkwiKCW4ZNSs2u11xBLJ1nUqR2xZVn5ICoE5NiiwYxCuP3oV0tHbDyiTrJD6bhCyVqNwlfr2mQRgt69x13oWtdQi3TcBKAuALu5BNc4kizG71QWWkAnkaRzxc93ZvydEM%2FyrxyG14dVHixNOtgOl7X2xvEDeCMFXXRaGsjHeDjGqmK2jMUC9ka7BsCHxyMshnuNFyognz3gtR%2BWK1dTMlzpuPDICn17tBE%2FFpZy32gKf86YoyfEdoW%2F4ljDIFbON%2Fpdh3orFKZz8nXCSJ2jXq6V4mpyIF%2FyoDRezAxZEhVOZPmSQyEnnuyLp49zGQ%3D%3D%7Ctkp%3ABFBM2I2H-v5n</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BME280 Pressure, Temperature and Humidity sensor</t>
   </si>
 </sst>
 </file>
@@ -926,38 +923,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
   <dimension ref="A1:M39"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.42578125" customWidth="1"/>
-    <col min="3" max="3" width="89.85546875" customWidth="1"/>
-    <col min="4" max="4" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.5703125" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" customWidth="1"/>
-    <col min="8" max="8" width="69.42578125" customWidth="1"/>
+    <col min="1" max="1" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.7265625" customWidth="1"/>
+    <col min="3" max="3" width="60.36328125" customWidth="1"/>
+    <col min="4" max="4" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.54296875" customWidth="1"/>
+    <col min="6" max="6" width="13.1796875" customWidth="1"/>
+    <col min="7" max="7" width="9.1796875" customWidth="1"/>
+    <col min="8" max="8" width="69.453125" customWidth="1"/>
     <col min="9" max="9" width="76" customWidth="1"/>
-    <col min="10" max="10" width="83.5703125" customWidth="1"/>
-    <col min="11" max="11" width="62.5703125" customWidth="1"/>
-    <col min="12" max="12" width="55.85546875" customWidth="1"/>
+    <col min="10" max="10" width="83.54296875" customWidth="1"/>
+    <col min="11" max="11" width="62.54296875" customWidth="1"/>
+    <col min="12" max="12" width="55.81640625" customWidth="1"/>
     <col min="13" max="13" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>17</v>
@@ -975,16 +972,16 @@
         <v>52</v>
       </c>
       <c r="K1" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M1" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="L1" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -995,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F2" s="3">
         <v>25.7</v>
@@ -1014,18 +1011,18 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F3" s="3">
         <v>2.52</v>
@@ -1041,7 +1038,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1052,7 +1049,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F4" s="3">
         <v>1.4</v>
@@ -1071,18 +1068,18 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F5" s="3">
         <v>11.96</v>
@@ -1098,18 +1095,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F6" s="3">
         <v>5.26</v>
@@ -1118,8 +1115,8 @@
         <f t="shared" si="0"/>
         <v>5.26</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>153</v>
+      <c r="H6" s="1" t="s">
+        <v>151</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>21</v>
@@ -1131,21 +1128,21 @@
         <v>60</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F7" s="3">
         <v>4.95</v>
@@ -1155,13 +1152,13 @@
         <v>4.95</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
@@ -1172,7 +1169,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F8" s="3">
         <v>15.2</v>
@@ -1185,7 +1182,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
@@ -1196,7 +1193,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F9" s="3">
         <v>5.25</v>
@@ -1215,18 +1212,18 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F10" s="3">
         <v>18</v>
@@ -1239,13 +1236,11 @@
         <v>25</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
@@ -1256,7 +1251,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F11" s="3">
         <v>1.0900000000000001</v>
@@ -1269,12 +1264,12 @@
         <v>26</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>9</v>
@@ -1283,7 +1278,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F12" s="3">
         <v>0.57999999999999996</v>
@@ -1296,21 +1291,21 @@
         <v>27</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="D13" s="2">
         <v>1</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F13" s="3">
         <v>0.14000000000000001</v>
@@ -1320,12 +1315,12 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="H13" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>146</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>10</v>
@@ -1334,7 +1329,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F14" s="3">
         <v>8.23</v>
@@ -1347,18 +1342,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F15" s="3">
         <v>8.24</v>
@@ -1368,36 +1363,36 @@
         <v>8.24</v>
       </c>
       <c r="H15" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J15" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="L15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M15" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D16" s="2">
         <v>1</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F16" s="3">
         <v>2.0299999999999998</v>
@@ -1410,21 +1405,21 @@
         <v>45</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D17" s="2">
         <v>1</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F17" s="3">
         <v>0.2</v>
@@ -1437,21 +1432,21 @@
         <v>28</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F18" s="3">
         <v>0.1</v>
@@ -1461,12 +1456,12 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>48</v>
@@ -1475,7 +1470,7 @@
         <v>3</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F19" s="3">
         <v>0.1</v>
@@ -1488,12 +1483,12 @@
         <v>50</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>47</v>
@@ -1502,7 +1497,7 @@
         <v>4</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F20" s="3">
         <v>0.1</v>
@@ -1515,21 +1510,21 @@
         <v>49</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D21" s="2">
         <v>2</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F21" s="3">
         <v>0.1</v>
@@ -1539,21 +1534,21 @@
         <v>0.2</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D22" s="2">
         <v>1</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F22" s="3">
         <v>0.39</v>
@@ -1566,21 +1561,21 @@
         <v>43</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D23" s="2">
         <v>1</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F23" s="3">
         <v>0.41</v>
@@ -1593,21 +1588,21 @@
         <v>34</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D24" s="2">
         <v>1</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F24" s="3">
         <v>0.26</v>
@@ -1620,12 +1615,12 @@
         <v>35</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>33</v>
@@ -1634,7 +1629,7 @@
         <v>4</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F25" s="3">
         <v>0.48</v>
@@ -1647,21 +1642,21 @@
         <v>29</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D26" s="2">
         <v>1</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F26" s="3">
         <v>3.58</v>
@@ -1674,13 +1669,13 @@
         <v>30</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>44</v>
       </c>
@@ -1691,7 +1686,7 @@
         <v>1</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F27" s="3">
         <v>60.76</v>
@@ -1701,21 +1696,21 @@
         <v>60.76</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D28" s="2">
         <v>1</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F28" s="3">
         <v>0.91</v>
@@ -1728,12 +1723,12 @@
         <v>31</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>38</v>
@@ -1742,7 +1737,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F29" s="3">
         <v>2.15</v>
@@ -1755,21 +1750,21 @@
         <v>37</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F30" s="3">
         <v>0.1</v>
@@ -1779,21 +1774,21 @@
         <v>0.1</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F31" s="3">
         <v>0.13</v>
@@ -1806,10 +1801,10 @@
         <v>42</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>39</v>
       </c>
@@ -1820,7 +1815,7 @@
         <v>9</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F32" s="3">
         <v>7.39</v>
@@ -1833,15 +1828,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D33" s="2">
         <v>2</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F33" s="3">
         <v>0.01</v>
@@ -1852,15 +1847,15 @@
       </c>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D34" s="2">
         <v>2</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F34" s="3">
         <v>0.01</v>
@@ -1871,15 +1866,15 @@
       </c>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D35" s="2">
         <v>2</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F35" s="3">
         <v>0.01</v>
@@ -1889,18 +1884,18 @@
         <v>0.02</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D36" s="2">
         <v>4</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F36" s="3">
         <v>7.2999999999999995E-2</v>
@@ -1910,21 +1905,21 @@
         <v>0.29199999999999998</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D37" s="2">
         <v>1</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F37" s="3">
         <v>2.68</v>
@@ -1934,21 +1929,21 @@
         <v>2.68</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D38" s="2">
         <v>1</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F38" s="3">
         <v>25</v>
@@ -1958,10 +1953,10 @@
         <v>25</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="F39" s="4" t="s">
         <v>14</v>
       </c>
@@ -1999,30 +1994,31 @@
     <hyperlink ref="J2" r:id="rId25" xr:uid="{85148DE2-C5FC-5645-B5BB-41BB837D9E5E}"/>
     <hyperlink ref="I5" r:id="rId26" xr:uid="{41DE90D8-7589-0C4B-AD96-FF698779CC02}"/>
     <hyperlink ref="K6" r:id="rId27" xr:uid="{50526146-D5B4-5C42-928A-1A4E698E0A66}"/>
-    <hyperlink ref="I10" r:id="rId28" display="https://www.ebay.com/itm/374993811392?chn=ps&amp;_trkparms=ispr%3D1&amp;amdata=enc%3A1tgCSJr3fRSKT8fAa1Y7Mgw25&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=374993811392&amp;targetid=2321110923741&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400684010&amp;mkgroupid=173029508068&amp;rlsatarget=pla-2321110923741&amp;abcId=9448486&amp;merchantid=6296724&amp;gad_source=1&amp;gad_campaignid=21400684010&amp;gbraid=0AAAAAD_QDh_duznfnFnLJIwhwQSUm0oBU&amp;gclid=EAIaIQobChMI3euy76jsjQMVFDQIBR3Brw42EAQYBSABEgL8OPD_BwE" xr:uid="{5370FA8F-6BA3-0A44-A70A-E9B0471E8594}"/>
-    <hyperlink ref="I19" r:id="rId29" xr:uid="{FAF305DA-B9D2-2244-A13B-6929AB49025C}"/>
-    <hyperlink ref="I26" r:id="rId30" xr:uid="{B99689F2-D490-2042-A4CC-3BA7CD9172AF}"/>
-    <hyperlink ref="H27" r:id="rId31" xr:uid="{1136733B-68A5-4A0B-995C-2A418A5AC777}"/>
-    <hyperlink ref="I3" r:id="rId32" display="https://www.ebay.com/itm/235081679206?chn=ps&amp;var=536091370095&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=536091370095_235081679206&amp;targetid=2295557532710&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400677539&amp;mkgroupid=173029508628&amp;rlsatarget=pla-2295557532710&amp;abcId=9448483&amp;merchantid=734150552&amp;gad_source=1&amp;gad_campaignid=21400677539&amp;gbraid=0AAAAAD_QDh9KZSet77KcrE8f9gL7cL_CG&amp;gclid=EAIaIQobChMIi8KGzaPsjQMVGEf_AR2yNzdrEAQYAyABEgL6F_D_BwE" xr:uid="{AD11255E-848C-4E6B-B235-2E174E495317}"/>
-    <hyperlink ref="H15" r:id="rId33" xr:uid="{DD127622-0F7B-0F49-8123-68EDBFB9D1FD}"/>
-    <hyperlink ref="I15" r:id="rId34" tooltip="https://www.staples.com/transcend-8gb-microsdhc-memory-card-class-10-ts8gusdhc10/product_IM1LK3226" xr:uid="{CD78FE6E-F962-024D-BECC-56B99B430391}"/>
-    <hyperlink ref="J15" r:id="rId35" tooltip="https://www.cdwg.com/product/transcend-flash-memory-card-8-gb-microsd/3181432?pfm=srh" xr:uid="{F7564EE8-2A81-B244-AEFD-6DA0DF39B5DC}"/>
-    <hyperlink ref="K15" r:id="rId36" tooltip="https://www.cdwg.com/product/kingston-industrial-flash-memory-card-8-gb-microsdhc-uhs-i/6669743?pfm=srh" xr:uid="{6EBC3D1F-2E28-7641-90A9-14D8B6437048}"/>
-    <hyperlink ref="H36" r:id="rId37" xr:uid="{AFFADB06-346C-4E3A-B07A-37D406DF404C}"/>
-    <hyperlink ref="H38" r:id="rId38" xr:uid="{EB0734B3-7C29-4D35-B394-905387802664}"/>
-    <hyperlink ref="H37" r:id="rId39" xr:uid="{26A48533-A061-40FE-A66E-723F0A8526D8}"/>
-    <hyperlink ref="H35" r:id="rId40" xr:uid="{327468E6-6FE8-4274-B476-C9C35280648B}"/>
-    <hyperlink ref="H30" r:id="rId41" display="https://www.digikey.com/en/products/detail/jst-sales-america-inc/B2B-XH-A/1651045?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20470400566&amp;gbraid=0AAAAADrbLljaCSzp9mL3BckOGUjmh-pLW&amp;gclid=CjwKCAiAoNbIBhB5EiwAZFbYGEhTlbpU8AtASh9T03rT2O-as-UbMvwFZowiONL1Xf91TSJaIz9zzBoCD-IQAvD_BwE" xr:uid="{A1578E18-966D-4A0B-89BB-AAA405790B24}"/>
-    <hyperlink ref="H7" r:id="rId42" xr:uid="{809BB693-6445-43CC-B4C1-47C121254BDE}"/>
-    <hyperlink ref="I7" r:id="rId43" xr:uid="{8E7D6AC4-E51D-48DC-AC39-840AA30DB295}"/>
-    <hyperlink ref="H21" r:id="rId44" xr:uid="{F2FBC813-F21B-4CA5-94D5-A1D3C7097891}"/>
-    <hyperlink ref="H13" r:id="rId45" xr:uid="{0C1E97B9-B29C-4292-84AE-9AEFCCB0C868}"/>
-    <hyperlink ref="H18" r:id="rId46" xr:uid="{51407470-A2C9-4C4E-89CA-FC24B70AF5A7}"/>
-    <hyperlink ref="I4" r:id="rId47" xr:uid="{1A2534D8-294F-4B39-89B1-8168C50C4225}"/>
-    <hyperlink ref="L6" r:id="rId48" xr:uid="{3B26DD18-290E-4BFE-BB80-46E0A92D8884}"/>
-    <hyperlink ref="J6" r:id="rId49" display="https://www.ebay.com/itm/223602242983?chn=ps&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=223602242983&amp;targetid=2295557532710&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400677539&amp;mkgroupid=173029508628&amp;rlsatarget=pla-2295557532710&amp;abcId=9448483&amp;merchantid=108461346&amp;gad_source=4&amp;gad_campaignid=21400677539&amp;gbraid=0AAAAAD_QDh9zBpIZmq8atlokvhUYT34hx&amp;gclid=EAIaIQobChMIyYbmlabsjQMVBjUIBR1KhTUNEAQYECABEgIh5fD_BwE" xr:uid="{8537022B-3B72-40E4-A752-C847F511BEE6}"/>
+    <hyperlink ref="I19" r:id="rId28" xr:uid="{FAF305DA-B9D2-2244-A13B-6929AB49025C}"/>
+    <hyperlink ref="I26" r:id="rId29" xr:uid="{B99689F2-D490-2042-A4CC-3BA7CD9172AF}"/>
+    <hyperlink ref="H27" r:id="rId30" xr:uid="{1136733B-68A5-4A0B-995C-2A418A5AC777}"/>
+    <hyperlink ref="I3" r:id="rId31" display="https://www.ebay.com/itm/235081679206?chn=ps&amp;var=536091370095&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=536091370095_235081679206&amp;targetid=2295557532710&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400677539&amp;mkgroupid=173029508628&amp;rlsatarget=pla-2295557532710&amp;abcId=9448483&amp;merchantid=734150552&amp;gad_source=1&amp;gad_campaignid=21400677539&amp;gbraid=0AAAAAD_QDh9KZSet77KcrE8f9gL7cL_CG&amp;gclid=EAIaIQobChMIi8KGzaPsjQMVGEf_AR2yNzdrEAQYAyABEgL6F_D_BwE" xr:uid="{AD11255E-848C-4E6B-B235-2E174E495317}"/>
+    <hyperlink ref="H15" r:id="rId32" xr:uid="{DD127622-0F7B-0F49-8123-68EDBFB9D1FD}"/>
+    <hyperlink ref="I15" r:id="rId33" tooltip="https://www.staples.com/transcend-8gb-microsdhc-memory-card-class-10-ts8gusdhc10/product_IM1LK3226" xr:uid="{CD78FE6E-F962-024D-BECC-56B99B430391}"/>
+    <hyperlink ref="J15" r:id="rId34" tooltip="https://www.cdwg.com/product/transcend-flash-memory-card-8-gb-microsd/3181432?pfm=srh" xr:uid="{F7564EE8-2A81-B244-AEFD-6DA0DF39B5DC}"/>
+    <hyperlink ref="K15" r:id="rId35" tooltip="https://www.cdwg.com/product/kingston-industrial-flash-memory-card-8-gb-microsdhc-uhs-i/6669743?pfm=srh" xr:uid="{6EBC3D1F-2E28-7641-90A9-14D8B6437048}"/>
+    <hyperlink ref="H36" r:id="rId36" xr:uid="{AFFADB06-346C-4E3A-B07A-37D406DF404C}"/>
+    <hyperlink ref="H38" r:id="rId37" xr:uid="{EB0734B3-7C29-4D35-B394-905387802664}"/>
+    <hyperlink ref="H37" r:id="rId38" xr:uid="{26A48533-A061-40FE-A66E-723F0A8526D8}"/>
+    <hyperlink ref="H35" r:id="rId39" xr:uid="{327468E6-6FE8-4274-B476-C9C35280648B}"/>
+    <hyperlink ref="H30" r:id="rId40" display="https://www.digikey.com/en/products/detail/jst-sales-america-inc/B2B-XH-A/1651045?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20470400566&amp;gbraid=0AAAAADrbLljaCSzp9mL3BckOGUjmh-pLW&amp;gclid=CjwKCAiAoNbIBhB5EiwAZFbYGEhTlbpU8AtASh9T03rT2O-as-UbMvwFZowiONL1Xf91TSJaIz9zzBoCD-IQAvD_BwE" xr:uid="{A1578E18-966D-4A0B-89BB-AAA405790B24}"/>
+    <hyperlink ref="H7" r:id="rId41" xr:uid="{809BB693-6445-43CC-B4C1-47C121254BDE}"/>
+    <hyperlink ref="I7" r:id="rId42" xr:uid="{8E7D6AC4-E51D-48DC-AC39-840AA30DB295}"/>
+    <hyperlink ref="H21" r:id="rId43" xr:uid="{F2FBC813-F21B-4CA5-94D5-A1D3C7097891}"/>
+    <hyperlink ref="H13" r:id="rId44" xr:uid="{0C1E97B9-B29C-4292-84AE-9AEFCCB0C868}"/>
+    <hyperlink ref="H18" r:id="rId45" xr:uid="{51407470-A2C9-4C4E-89CA-FC24B70AF5A7}"/>
+    <hyperlink ref="I4" r:id="rId46" xr:uid="{1A2534D8-294F-4B39-89B1-8168C50C4225}"/>
+    <hyperlink ref="L6" r:id="rId47" xr:uid="{3B26DD18-290E-4BFE-BB80-46E0A92D8884}"/>
+    <hyperlink ref="J6" r:id="rId48" display="https://www.ebay.com/itm/223602242983?chn=ps&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=223602242983&amp;targetid=2295557532710&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400677539&amp;mkgroupid=173029508628&amp;rlsatarget=pla-2295557532710&amp;abcId=9448483&amp;merchantid=108461346&amp;gad_source=4&amp;gad_campaignid=21400677539&amp;gbraid=0AAAAAD_QDh9zBpIZmq8atlokvhUYT34hx&amp;gclid=EAIaIQobChMIyYbmlabsjQMVBjUIBR1KhTUNEAQYECABEgIh5fD_BwE" xr:uid="{8537022B-3B72-40E4-A752-C847F511BEE6}"/>
+    <hyperlink ref="I10" r:id="rId49" xr:uid="{637C6DC6-6221-421C-AA28-8557881CF9FD}"/>
+    <hyperlink ref="H6" r:id="rId50" display="https://www.ebay.com/itm/327147846952?_skw=BME280+5+V&amp;itmmeta=01KZVT1RTW26G1WWC3Y7NSNY2T&amp;hash=item4c2b87fd28:g:P1MAAeSwcWdp~jCK&amp;itmprp=enc%3AAQALAAAA8GfYFPkwiKCW4ZNSs2u11xBLJ1nUqR2xZVn5ICoE5NiiwYxCuP3oV0tHbDyiTrJD6bhCyVqNwlfr2mQRgt69x13oWtdQi3TcBKAuALu5BNc4kizG71QWWkAnkaRzxc93ZvydEM%2FyrxyG14dVHixNOtgOl7X2xvEDeCMFXXRaGsjHeDjGqmK2jMUC9ka7BsCHxyMshnuNFyognz3gtR%2BWK1dTMlzpuPDICn17tBE%2FFpZy32gKf86YoyfEdoW%2F4ljDIFbON%2Fpdh3orFKZz8nXCSJ2jXq6V4mpyIF%2FyoDRezAxZEhVOZPmSQyEnnuyLp49zGQ%3D%3D%7Ctkp%3ABFBM2I2H-v5n" xr:uid="{B10E6281-8922-4D98-84C4-5D848CF9F0D8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId50"/>
+  <pageSetup orientation="portrait" r:id="rId51"/>
 </worksheet>
 </file>